--- a/Analysis/04_Robust_Core_and_Policy/8_classification_comparison.xlsx
+++ b/Analysis/04_Robust_Core_and_Policy/8_classification_comparison.xlsx
@@ -585,7 +585,7 @@
         <v>0.9991025623614186</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6807152591960837</v>
+        <v>0.6673676674308086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
         <v>0.9838709677419355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -608,13 +608,13 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9510659992132624</v>
+        <v>0.9593724101911646</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9352104189614698</v>
+        <v>0.9474281405794532</v>
       </c>
       <c r="M2" t="n">
         <v>0.5149786364148489</v>
@@ -638,7 +638,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8398321596762245</v>
+        <v>0.851703523715019</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7552</v>
+        <v>0.8013</v>
       </c>
       <c r="AC2" t="n">
         <v>10000</v>
@@ -688,7 +688,7 @@
         <v>0.5192477741383978</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9532967073477324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -711,13 +711,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8980265101338745</v>
+        <v>0.8907549207409081</v>
       </c>
       <c r="K3" t="n">
         <v>0.8064516129032258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8522390615185501</v>
+        <v>0.8486032668220669</v>
       </c>
       <c r="M3" t="n">
         <v>0.5149786364148489</v>
@@ -741,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7169949325357213</v>
+        <v>0.715544534416482</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -755,19 +755,19 @@
         <v>4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
         <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8998</v>
+        <v>0.781</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0776</v>
+        <v>0.0565</v>
       </c>
       <c r="AC3" t="n">
         <v>10000</v>
@@ -791,7 +791,7 @@
         <v>0.4979197589098577</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6999165700575044</v>
+        <v>0.6877786171594643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6872470066955473</v>
+        <v>0.6891401350813889</v>
       </c>
       <c r="U4" t="n">
         <v>0.5</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2704901543845801</v>
+        <v>0.268462179680248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>0.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4956353247070321</v>
+        <v>0.4937913092249533</v>
       </c>
       <c r="U5" t="n">
         <v>0.2083333333333333</v>
@@ -961,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>33.5</v>
+        <v>33</v>
       </c>
       <c r="Y5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>39</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0379</v>
+        <v>0.0405</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
         <v>0.4673013212109958</v>
       </c>
       <c r="C6" t="n">
-        <v>0.687641460034852</v>
+        <v>0.6664622042958805</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>0.6935483870967742</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8054832896247596</v>
+        <v>0.7985092770636493</v>
       </c>
       <c r="K6" t="n">
         <v>0.6935483870967742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.749515838360767</v>
+        <v>0.7460288320802118</v>
       </c>
       <c r="M6" t="n">
         <v>0.5149786364148489</v>
@@ -1050,7 +1050,7 @@
         <v>0.1875</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6498234686370755</v>
+        <v>0.6517701551822085</v>
       </c>
       <c r="U6" t="n">
         <v>0.1875</v>
@@ -1064,16 +1064,16 @@
         <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5906</v>
+        <v>0.6079</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0005</v>
@@ -1093,43 +1093,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sec43</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5740291262162156</v>
+        <v>0.2437325716404674</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3586092338007782</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Strategic Core Sectors</t>
+          <t>Emerging Leverage Sectors</t>
         </is>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6935483870967742</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7914738158958257</v>
+        <v>0.5236349380886428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7425111014963</v>
+        <v>0.3989142432378698</v>
       </c>
       <c r="M7" t="n">
         <v>0.5149786364148489</v>
@@ -1138,25 +1138,25 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P7" t="n">
         <v>96</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1.9375</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5303868726187789</v>
+        <v>0.4040290293722089</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1354166666666667</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1164,22 +1164,22 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0399</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.1361</v>
       </c>
       <c r="AC7" t="n">
         <v>10000</v>
@@ -1189,21 +1189,21 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Mean-core, not robust-core</t>
+          <t>Non-core in robust method</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sec5</t>
+          <t>sec43</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4614857629836915</v>
+        <v>0.5740291262162156</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6079501653753897</v>
+        <v>0.3517799565730474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1211,28 +1211,28 @@
         </is>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7822164937407833</v>
+        <v>0.7914738158958257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7298179242897465</v>
+        <v>0.7425111014963</v>
       </c>
       <c r="M8" t="n">
         <v>0.5149786364148489</v>
@@ -1247,16 +1247,16 @@
         <v>96</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3125</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6492930061484815</v>
+        <v>0.5300261258107251</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>30.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.9879</v>
+        <v>0.0413</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0015</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>10000</v>
@@ -1299,14 +1299,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sec38</t>
+          <t>sec5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4958635433072648</v>
+        <v>0.4614857629836915</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3645501609885945</v>
+        <v>0.5903679542265067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7334720645743273</v>
+        <v>0.7822164937407833</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="L9" t="n">
-        <v>0.721574741964583</v>
+        <v>0.7298179242897465</v>
       </c>
       <c r="M9" t="n">
         <v>0.5149786364148489</v>
@@ -1350,42 +1350,42 @@
         <v>96</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6451065037373119</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Not Robust Core</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.5313066598936588</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Not Robust Core</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>34</v>
-      </c>
       <c r="Y9" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.9877</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="AC9" t="n">
         <v>10000</v>
@@ -1402,14 +1402,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sec9</t>
+          <t>sec38</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5244586006161442</v>
+        <v>0.4958635433072648</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3491353097578615</v>
+        <v>0.3584420048627939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.7580645161290323</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -1432,13 +1432,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7284896639120139</v>
+        <v>0.7334720645743273</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6868254771172972</v>
+        <v>0.721574741964583</v>
       </c>
       <c r="M10" t="n">
         <v>0.5149786364148489</v>
@@ -1453,16 +1453,16 @@
         <v>96</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.875</v>
+        <v>3.0625</v>
       </c>
       <c r="R10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4932492440649006</v>
+        <v>0.5334742604231651</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1476,16 +1476,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.75</v>
+        <v>32.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1505,28 +1505,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sec35</t>
+          <t>sec9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5460897795721134</v>
+        <v>0.5244586006161442</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3051754999736183</v>
+        <v>0.3425613430432314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Strategic Core Sectors</t>
         </is>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7142448330801462</v>
+        <v>0.7284896639120139</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6555095133142667</v>
+        <v>0.6868254771172972</v>
       </c>
       <c r="M11" t="n">
         <v>0.5149786364148489</v>
@@ -1556,7 +1556,7 @@
         <v>96</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.25</v>
+        <v>3.875</v>
       </c>
       <c r="R11" t="n">
         <v>4</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.455045059405897</v>
+        <v>0.4954725812870177</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.009900000000000001</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1601,50 +1601,50 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Non-core in robust method</t>
+          <t>Mean-core, not robust-core</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sec49</t>
+          <t>sec35</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4313568075982206</v>
+        <v>0.5460897795721134</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3862613489018079</v>
+        <v>0.3004656854004149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Strategic Core Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E12" t="b">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6743401600118346</v>
+        <v>0.7142448330801462</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6436216929091432</v>
+        <v>0.6555095133142667</v>
       </c>
       <c r="M12" t="n">
         <v>0.5149786364148489</v>
@@ -1659,7 +1659,7 @@
         <v>96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.625</v>
+        <v>4.25</v>
       </c>
       <c r="R12" t="n">
         <v>4</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4359106203729063</v>
+        <v>0.4567928886854214</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1682,16 +1682,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
         <v>41</v>
       </c>
-      <c r="Y12" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>48</v>
-      </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1704,50 +1704,50 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Mean-core, not robust-core</t>
+          <t>Non-core in robust method</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sec41</t>
+          <t>sec49</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5803712152869871</v>
+        <v>0.4313568075982206</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2919390133642236</v>
+        <v>0.3788695124995178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Strategic Core Sectors</t>
         </is>
       </c>
       <c r="E13" t="b">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7204100462621708</v>
+        <v>0.6743401600118346</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6424630876472144</v>
+        <v>0.6436216929091432</v>
       </c>
       <c r="M13" t="n">
         <v>0.5149786364148489</v>
@@ -1762,16 +1762,16 @@
         <v>96</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>3.5625</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5176870393148046</v>
+        <v>0.4371383425573418</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>40.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.271</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Non-core in robust method</t>
+          <t>Mean-core, not robust-core</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
         <v>0.4797537860769988</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3052956060557226</v>
+        <v>0.303244589262894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.471418117668666</v>
+        <v>0.4726157760652588</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1888,16 +1888,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>27.25</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -1917,14 +1917,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sec52</t>
+          <t>sec41</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5031558988234257</v>
+        <v>0.5803712152869871</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2438275268357347</v>
+        <v>0.2856338358151407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1932,28 +1932,28 @@
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6080024782248633</v>
+        <v>0.7100438936469399</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5378722068543671</v>
+        <v>0.6292154952105666</v>
       </c>
       <c r="M15" t="n">
         <v>0.5149786364148489</v>
@@ -1968,16 +1968,16 @@
         <v>96</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.1875</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3444547708060358</v>
+        <v>0.5171237341742774</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1988,19 +1988,19 @@
         </is>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>15.25</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.163</v>
+        <v>0.2672</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2020,43 +2020,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sec37</t>
+          <t>sec52</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3573892771216133</v>
+        <v>0.5031558988234257</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4354184408183513</v>
+        <v>0.2423505753028637</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6094981815384253</v>
+        <v>0.6080024782248633</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5305555423821159</v>
+        <v>0.5378722068543671</v>
       </c>
       <c r="M16" t="n">
         <v>0.5149786364148489</v>
@@ -2071,16 +2071,16 @@
         <v>96</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3910684443734605</v>
+        <v>0.3292699865317814</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2094,16 +2094,16 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49</v>
+        <v>15.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.1634</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2123,14 +2123,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sec59</t>
+          <t>sec37</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3586262947560303</v>
+        <v>0.3573892771216133</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3567103628751925</v>
+        <v>0.4257551734075429</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,25 +2141,25 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5629009150521015</v>
+        <v>0.6154446460754488</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5153214252679862</v>
+        <v>0.5335287746506276</v>
       </c>
       <c r="M17" t="n">
         <v>0.5149786364148489</v>
@@ -2174,16 +2174,16 @@
         <v>96</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>3.6875</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3339370198597932</v>
+        <v>0.392160574024591</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2197,13 +2197,13 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39</v>
+        <v>47.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="Z17" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2226,14 +2226,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sec36</t>
+          <t>sec59</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3402528503553442</v>
+        <v>0.3586262947560303</v>
       </c>
       <c r="C18" t="n">
-        <v>0.725285409898355</v>
+        <v>0.3496673999461191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,25 +2244,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="G18" t="n">
-        <v>0.967741935483871</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6246747332592607</v>
+        <v>0.5629009150521015</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5139502698554368</v>
+        <v>0.5153214252679862</v>
       </c>
       <c r="M18" t="n">
         <v>0.5149786364148489</v>
@@ -2277,16 +2277,16 @@
         <v>96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8125</v>
+        <v>5.3125</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4269313166669862</v>
+        <v>0.3340589217742469</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2297,22 +2297,22 @@
         </is>
       </c>
       <c r="W18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>5.75</v>
+        <v>39.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.9077</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>10000</v>
@@ -2329,43 +2329,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sec45</t>
+          <t>sec36</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4723605407333147</v>
+        <v>0.3402528503553442</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2387074095046538</v>
+        <v>0.7017334206753636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Emerging Leverage Sectors</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5661267346704595</v>
+        <v>0.6246747332592607</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="L19" t="n">
-        <v>0.508869818948133</v>
+        <v>0.5139502698554368</v>
       </c>
       <c r="M19" t="n">
         <v>0.5149786364148489</v>
@@ -2380,16 +2380,16 @@
         <v>96</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.25</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3736737102833727</v>
+        <v>0.4249541220079154</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X19" t="n">
-        <v>31.25</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>0.9084</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="AC19" t="n">
         <v>10000</v>
@@ -2432,14 +2432,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sec42</t>
+          <t>sec45</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3858117471125858</v>
+        <v>0.4723605407333147</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2779298333235067</v>
+        <v>0.2388865917540891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,28 +2447,28 @@
         </is>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="G20" t="n">
-        <v>0.532258064516129</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5074881523403959</v>
+        <v>0.5661267346704595</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4956795600411657</v>
+        <v>0.508869818948133</v>
       </c>
       <c r="M20" t="n">
         <v>0.5149786364148489</v>
@@ -2483,7 +2483,7 @@
         <v>96</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.5</v>
+        <v>6.1875</v>
       </c>
       <c r="R20" t="n">
         <v>6</v>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4100949544135749</v>
+        <v>0.3763167729535922</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Z20" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2535,14 +2535,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sec33</t>
+          <t>sec42</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.571895336520327</v>
+        <v>0.3858117471125858</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2175647468418478</v>
+        <v>0.2809115919090762</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,28 +2550,28 @@
         </is>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.555925417406906</v>
+        <v>0.5074881523403959</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4553820635421627</v>
+        <v>0.4956795600411657</v>
       </c>
       <c r="M21" t="n">
         <v>0.5149786364148489</v>
@@ -2586,16 +2586,16 @@
         <v>96</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3013459807115512</v>
+        <v>0.4089710771463228</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2606,19 +2606,19 @@
         </is>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>8.25</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2638,14 +2638,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sec34</t>
+          <t>sec33</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6876809642844807</v>
+        <v>0.571895336520327</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2108879095649088</v>
+        <v>0.2191461141217687</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2656,25 +2656,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5629009150521015</v>
+        <v>0.5684196834421321</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4508052962357282</v>
+        <v>0.469693712688808</v>
       </c>
       <c r="M22" t="n">
         <v>0.5149786364148489</v>
@@ -2689,39 +2689,39 @@
         <v>96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8125</v>
+        <v>4.3125</v>
       </c>
       <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.2869279044313761</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Not Robust Core</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
         <v>3</v>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.390906737002899</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Not Robust Core</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
-        <v>2</v>
-      </c>
       <c r="X22" t="n">
-        <v>11.75</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2398</v>
+        <v>0.6797</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         <v>0.4210691445796353</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2298714811555191</v>
+        <v>0.2284728763831992</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>0.5967741935483871</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
@@ -2771,13 +2771,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4905453653466306</v>
+        <v>0.5002600780409944</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4468855858991218</v>
+        <v>0.4598074583753359</v>
       </c>
       <c r="M23" t="n">
         <v>0.5149786364148489</v>
@@ -2792,16 +2792,16 @@
         <v>96</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.25</v>
+        <v>7.1875</v>
       </c>
       <c r="R23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.335455355095027</v>
+        <v>0.3323886224161811</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2815,13 +2815,13 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Z23" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2844,43 +2844,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sec28</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.312304950478526</v>
+        <v>0.6876809642844807</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3534367245500948</v>
+        <v>0.2178040069082643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4952952429930351</v>
+        <v>0.5629009150521015</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4331314924642595</v>
+        <v>0.4508052962357282</v>
       </c>
       <c r="M24" t="n">
         <v>0.5149786364148489</v>
@@ -2895,16 +2895,16 @@
         <v>96</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.625</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3880291258814029</v>
+        <v>0.4116992154725374</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         </is>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X24" t="n">
-        <v>19.75</v>
+        <v>9.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.1585</v>
+        <v>0.5475</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -2947,28 +2947,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sec26</t>
+          <t>sec28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4201874006564538</v>
+        <v>0.312304950478526</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2220682041745093</v>
+        <v>0.3455016300708108</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Emerging Leverage Sectors</t>
         </is>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
@@ -2977,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4740947889257764</v>
+        <v>0.4952952429930351</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4305957815596624</v>
+        <v>0.4331314924642595</v>
       </c>
       <c r="M25" t="n">
         <v>0.5149786364148489</v>
@@ -2998,7 +2998,7 @@
         <v>96</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.25</v>
+        <v>4.6875</v>
       </c>
       <c r="R25" t="n">
         <v>5</v>
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3736009740936068</v>
+        <v>0.3871053288160953</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3021,16 +3021,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>47</v>
+        <v>18.75</v>
       </c>
       <c r="Y25" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3050,28 +3050,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sec32</t>
+          <t>sec26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3186192870869954</v>
+        <v>0.4201874006564538</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2596311384999733</v>
+        <v>0.2221592524772774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Peripheral Limited-Impact Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.3870967741935484</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.5</v>
       </c>
       <c r="H26" t="n">
         <v>7</v>
@@ -3080,13 +3080,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4399413450640599</v>
+        <v>0.4740947889257764</v>
       </c>
       <c r="K26" t="n">
         <v>0.3870967741935484</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4135190596288041</v>
+        <v>0.4305957815596624</v>
       </c>
       <c r="M26" t="n">
         <v>0.5149786364148489</v>
@@ -3101,16 +3101,16 @@
         <v>96</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.625</v>
+        <v>5.3125</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2858225982219578</v>
+        <v>0.3783554806126725</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3124,16 +3124,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>36.25</v>
+        <v>44.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Z26" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3153,43 +3153,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sec23</t>
+          <t>sec32</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4147371809959374</v>
+        <v>0.3186192870869954</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2194290416440928</v>
+        <v>0.2672659967173641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="E27" t="b">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4510364985196633</v>
+        <v>0.4399413450640599</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4110021202275736</v>
+        <v>0.4135190596288041</v>
       </c>
       <c r="M27" t="n">
         <v>0.5149786364148489</v>
@@ -3204,7 +3204,7 @@
         <v>96</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.375</v>
+        <v>7.6875</v>
       </c>
       <c r="R27" t="n">
         <v>7.5</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3157044933685694</v>
+        <v>0.2863153700661756</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3227,16 +3227,16 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>42.25</v>
+        <v>36.25</v>
       </c>
       <c r="Y27" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Z27" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>0.3122354370967021</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2901793879337969</v>
+        <v>0.286029281447945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         <v>0.3548387096774194</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="H28" t="n">
         <v>8</v>
@@ -3286,13 +3286,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4411223977799143</v>
+        <v>0.4475624814681164</v>
       </c>
       <c r="K28" t="n">
         <v>0.3548387096774194</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3979805537286668</v>
+        <v>0.4012005955727679</v>
       </c>
       <c r="M28" t="n">
         <v>0.5149786364148489</v>
@@ -3307,7 +3307,7 @@
         <v>96</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.875</v>
+        <v>7</v>
       </c>
       <c r="R28" t="n">
         <v>7</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3020179084702055</v>
+        <v>0.3004519071920598</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3330,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>32.5</v>
+        <v>34.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -3359,43 +3359,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2437325716404674</v>
+        <v>0.4147371809959374</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9904446051399636</v>
+        <v>0.2185694541420376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5193949092936974</v>
+        <v>0.4411223977799143</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3967942288403971</v>
+        <v>0.3979805537286668</v>
       </c>
       <c r="M29" t="n">
         <v>0.5149786364148489</v>
@@ -3410,16 +3410,16 @@
         <v>96</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>7.3125</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4037383703191089</v>
+        <v>0.3128054375760965</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3430,22 +3430,22 @@
         </is>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>5.5</v>
+        <v>43.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8641</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1588</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>10000</v>
@@ -3469,7 +3469,7 @@
         <v>0.2577236561154611</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4356857864518975</v>
+        <v>0.4249839345544715</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3483,22 +3483,22 @@
         <v>0.2903225806451613</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4934535013154308</v>
+        <v>0.4886857228239715</v>
       </c>
       <c r="K30" t="n">
         <v>0.2903225806451613</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3918880409802961</v>
+        <v>0.3895041517345664</v>
       </c>
       <c r="M30" t="n">
         <v>0.5149786364148489</v>
@@ -3513,7 +3513,7 @@
         <v>96</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.0625</v>
+        <v>4.3125</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
@@ -3522,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3180899789181111</v>
+        <v>0.3181711994485628</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3536,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>52</v>
+        <v>51.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Z30" t="n">
         <v>54</v>
@@ -3572,7 +3572,7 @@
         <v>0.5720659109364322</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1894662942222624</v>
+        <v>0.1872395685478882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>96</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8125</v>
+        <v>4.0625</v>
       </c>
       <c r="R31" t="n">
         <v>4</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3166889000033498</v>
+        <v>0.3184478580547956</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3639,16 +3639,16 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>25.5</v>
+        <v>25.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z31" t="n">
         <v>37</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.0128</v>
+        <v>0.0135</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0.4457272972203258</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1968516465199397</v>
+        <v>0.1981355867772255</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>96</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.6875</v>
+        <v>6.75</v>
       </c>
       <c r="R32" t="n">
         <v>7</v>
@@ -3728,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2877740689793272</v>
+        <v>0.2782182739384375</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3742,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>29.25</v>
+        <v>28.75</v>
       </c>
       <c r="Y32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0.4170667833707113</v>
       </c>
       <c r="C33" t="n">
-        <v>0.202872894827944</v>
+        <v>0.2030655108169831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>96</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.5625</v>
+        <v>8.5</v>
       </c>
       <c r="R33" t="n">
         <v>9</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2864307108883727</v>
+        <v>0.2853415849598518</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>46</v>
+        <v>45.25</v>
       </c>
       <c r="Y33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z33" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         <v>0.2621114898251326</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3255569877438948</v>
+        <v>0.3197704244775977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,16 +3925,16 @@
         <v>96</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.625</v>
+        <v>6.3125</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2768223314380032</v>
+        <v>0.277205628101355</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3948,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>45.5</v>
+        <v>47.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Z34" t="n">
         <v>52</v>
@@ -3984,7 +3984,7 @@
         <v>0.2768163573956286</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2506868199584197</v>
+        <v>0.2469687660146793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,16 +4028,16 @@
         <v>96</v>
       </c>
       <c r="Q35" t="n">
-        <v>8.4375</v>
+        <v>8.5625</v>
       </c>
       <c r="R35" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.260657148558256</v>
+        <v>0.2580102415586481</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4051,16 +4051,16 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y35" t="n">
         <v>11</v>
       </c>
       <c r="Z35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1793</v>
+        <v>0.138</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>0.2421716836672591</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4008295848939624</v>
+        <v>0.3912826609771002</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>0.7741935483870968</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>96</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.125</v>
+        <v>5.375</v>
       </c>
       <c r="R36" t="n">
         <v>5</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0.2712828164482995</v>
+        <v>0.2716902152452729</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
         <v>55</v>
       </c>
       <c r="Y36" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z36" t="n">
         <v>57</v>
@@ -4183,43 +4183,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sec6</t>
+          <t>sec4</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2194971222998793</v>
+        <v>0.4576525581557085</v>
       </c>
       <c r="C37" t="n">
-        <v>0.452172605952452</v>
+        <v>0.1846218812499254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4393496281250399</v>
+        <v>0.4131047895117967</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3325780398689716</v>
+        <v>0.3355846528204145</v>
       </c>
       <c r="M37" t="n">
         <v>0.5149786364148489</v>
@@ -4237,13 +4237,13 @@
         <v>5.4375</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0.2881182264533089</v>
+        <v>0.3133526207040953</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4254,19 +4254,19 @@
         </is>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>27.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Z37" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.7398</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -4286,14 +4286,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sec61</t>
+          <t>sec6</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2012943077208449</v>
+        <v>0.2194971222998793</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4570770776682223</v>
+        <v>0.4581891321377697</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="G38" t="n">
         <v>0.8709677419354839</v>
@@ -4316,13 +4316,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.427343267725541</v>
+        <v>0.4434750672537909</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3185103435401899</v>
+        <v>0.3346407594333471</v>
       </c>
       <c r="M38" t="n">
         <v>0.5149786364148489</v>
@@ -4337,16 +4337,16 @@
         <v>96</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>5.4375</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.2355695179933592</v>
+        <v>0.2872053292521712</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X38" t="n">
-        <v>53.25</v>
+        <v>9.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.7333</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -4389,28 +4389,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sec4</t>
+          <t>sec61</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4576525581557085</v>
+        <v>0.2012943077208449</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1780530787239071</v>
+        <v>0.4449838259858848</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Emerging Leverage Sectors</t>
         </is>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="H39" t="n">
         <v>6</v>
@@ -4419,13 +4419,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3864241467971271</v>
+        <v>0.4233678951098931</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3061152992050151</v>
+        <v>0.3165226572323659</v>
       </c>
       <c r="M39" t="n">
         <v>0.5149786364148489</v>
@@ -4440,16 +4440,16 @@
         <v>96</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.375</v>
+        <v>4.1875</v>
       </c>
       <c r="R39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3054443837257906</v>
+        <v>0.2358520815452914</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -4463,13 +4463,13 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>32.75</v>
+        <v>53</v>
       </c>
       <c r="Y39" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Z39" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -4492,14 +4492,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sec54</t>
+          <t>sec11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3969602551421552</v>
+        <v>0.4117293923828608</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1533484256509779</v>
+        <v>0.1568547508210429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="G40" t="n">
         <v>0.1935483870967742</v>
@@ -4522,13 +4522,13 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3160631926171842</v>
+        <v>0.3209636893892323</v>
       </c>
       <c r="K40" t="n">
         <v>0.1935483870967742</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2548057898569792</v>
+        <v>0.2572560382430032</v>
       </c>
       <c r="M40" t="n">
         <v>0.5149786364148489</v>
@@ -4543,16 +4543,16 @@
         <v>96</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.875</v>
+        <v>7.4375</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.1990189245797232</v>
+        <v>0.22134654523134</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y40" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z40" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.2029</v>
+        <v>0.0849</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0.1642480739396937</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5503618575209929</v>
+        <v>0.5340638320583172</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>96</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.75</v>
+        <v>3.625</v>
       </c>
       <c r="R41" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2031563330930526</v>
+        <v>0.2039278319360105</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -4669,10 +4669,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>61.25</v>
+        <v>61</v>
       </c>
       <c r="Y41" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z41" t="n">
         <v>62</v>
@@ -4698,28 +4698,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sec11</t>
+          <t>sec40</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4117293923828608</v>
+        <v>0.2778156957304661</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1494065809172398</v>
+        <v>0.177170348027705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.532258064516129</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="H42" t="n">
         <v>9</v>
@@ -4728,13 +4728,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3072993368267363</v>
+        <v>0.2664953490622307</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="L42" t="n">
-        <v>0.242359345832723</v>
+        <v>0.2380863842085347</v>
       </c>
       <c r="M42" t="n">
         <v>0.5149786364148489</v>
@@ -4749,16 +4749,16 @@
         <v>96</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.5625</v>
+        <v>9.4375</v>
       </c>
       <c r="R42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0.2221335139506481</v>
+        <v>0.2389705469469401</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -4772,16 +4772,16 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>17.75</v>
+        <v>41.75</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Z42" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         <v>0.2201482470760719</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1837913236988149</v>
+        <v>0.1844420786764618</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>0.2419354838709677</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="H43" t="n">
         <v>10</v>
@@ -4831,13 +4831,13 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2337318830030555</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2297691673079794</v>
       </c>
       <c r="M43" t="n">
         <v>0.5149786364148489</v>
@@ -4852,16 +4852,16 @@
         <v>96</v>
       </c>
       <c r="Q43" t="n">
-        <v>10.125</v>
+        <v>10.0625</v>
       </c>
       <c r="R43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1818552595380997</v>
+        <v>0.183731945911948</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4872,19 +4872,19 @@
         </is>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="Y43" t="n">
         <v>10</v>
       </c>
       <c r="Z43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.4497</v>
+        <v>0.4194</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -4904,14 +4904,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sec40</t>
+          <t>sec18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2778156957304661</v>
+        <v>0.344953665673041</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1729904246625682</v>
+        <v>0.1506541191950277</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4919,28 +4919,28 @@
         </is>
       </c>
       <c r="E44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="H44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.2664953490622307</v>
+        <v>0.2727666858917381</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2380863842085347</v>
+        <v>0.2250930203652239</v>
       </c>
       <c r="M44" t="n">
         <v>0.5149786364148489</v>
@@ -4955,7 +4955,7 @@
         <v>96</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.5</v>
+        <v>9.375</v>
       </c>
       <c r="R44" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.2357281953359902</v>
+        <v>0.1886622025770425</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4978,13 +4978,13 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>44.75</v>
+        <v>23.75</v>
       </c>
       <c r="Y44" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -5007,14 +5007,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sec13</t>
+          <t>sec54</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4358270731870135</v>
+        <v>0.3969602551421552</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1424196174441631</v>
+        <v>0.1477695730282641</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,28 +5022,28 @@
         </is>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.3021773225031483</v>
+        <v>0.2885249003225535</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2236693064128645</v>
+        <v>0.2249076114515993</v>
       </c>
       <c r="M45" t="n">
         <v>0.5149786364148489</v>
@@ -5058,16 +5058,16 @@
         <v>96</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.3125</v>
+        <v>7.0625</v>
       </c>
       <c r="R45" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0.207973305673642</v>
+        <v>0.2047463754114916</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -5081,16 +5081,16 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>28.25</v>
+        <v>20.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Z45" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.0541</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -5110,43 +5110,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sec18</t>
+          <t>sec13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.344953665673041</v>
+        <v>0.4358270731870135</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1490209874277699</v>
+        <v>0.144840916178343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Peripheral Limited-Impact Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2600728305902758</v>
+        <v>0.3021773225031483</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2106815765854605</v>
+        <v>0.2236693064128645</v>
       </c>
       <c r="M46" t="n">
         <v>0.5149786364148489</v>
@@ -5161,16 +5161,16 @@
         <v>96</v>
       </c>
       <c r="Q46" t="n">
-        <v>9.625</v>
+        <v>7.3125</v>
       </c>
       <c r="R46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1858950457604397</v>
+        <v>0.2065191927927434</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>22</v>
+        <v>29.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z46" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>0.1260795490030864</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3882176841884978</v>
+        <v>0.3794793146420848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>0.7580645161290323</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>96</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.125</v>
+        <v>6.375</v>
       </c>
       <c r="R47" t="n">
         <v>6</v>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.159159547359622</v>
+        <v>0.1590250643308663</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -5287,13 +5287,13 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
       </c>
       <c r="Z47" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -5316,43 +5316,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sec21</t>
+          <t>sec10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1749672391619654</v>
+        <v>0.3948146948073902</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1841962711555078</v>
+        <v>0.1366155674761129</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Peripheral Limited-Impact Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="H48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2040179135592503</v>
+        <v>0.254000254000381</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1826541180699477</v>
+        <v>0.1915162560324486</v>
       </c>
       <c r="M48" t="n">
         <v>0.5149786364148489</v>
@@ -5367,16 +5367,16 @@
         <v>96</v>
       </c>
       <c r="Q48" t="n">
-        <v>10.5625</v>
+        <v>8.4375</v>
       </c>
       <c r="R48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0.1502746221789604</v>
+        <v>0.1604834826879845</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -5390,13 +5390,13 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="Y48" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="Z48" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -5419,14 +5419,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sec17</t>
+          <t>sec21</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1605653387579659</v>
+        <v>0.1749672391619654</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2323095089965548</v>
+        <v>0.1845847231173738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="H49" t="n">
         <v>10</v>
@@ -5449,13 +5449,13 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2326162113202574</v>
+        <v>0.1975394953857402</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1808242346923867</v>
+        <v>0.1794149089831927</v>
       </c>
       <c r="M49" t="n">
         <v>0.5149786364148489</v>
@@ -5470,16 +5470,16 @@
         <v>96</v>
       </c>
       <c r="Q49" t="n">
-        <v>8.75</v>
+        <v>10.5625</v>
       </c>
       <c r="R49" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.197356595135165</v>
+        <v>0.1503511582038062</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5493,13 +5493,13 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>57.25</v>
+        <v>51.75</v>
       </c>
       <c r="Y49" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="Z49" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -5522,28 +5522,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sec10</t>
+          <t>sec17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3948146948073902</v>
+        <v>0.1605653387579659</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1326242266161869</v>
+        <v>0.228470072656473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="E50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="H50" t="n">
         <v>10</v>
@@ -5552,13 +5552,13 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2375954816557457</v>
+        <v>0.2280989616730798</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1752493537310987</v>
+        <v>0.178565609868798</v>
       </c>
       <c r="M50" t="n">
         <v>0.5149786364148489</v>
@@ -5573,7 +5573,7 @@
         <v>96</v>
       </c>
       <c r="Q50" t="n">
-        <v>8.4375</v>
+        <v>8.9375</v>
       </c>
       <c r="R50" t="n">
         <v>9</v>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1767495057521257</v>
+        <v>0.1958168990437883</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5596,13 +5596,13 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>34.75</v>
+        <v>57.5</v>
       </c>
       <c r="Y50" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="Z50" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
         <v>0.09327935949424218</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4294680258827999</v>
+        <v>0.4188678913364022</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>96</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.0625</v>
+        <v>5.3125</v>
       </c>
       <c r="R51" t="n">
         <v>5</v>
@@ -5685,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1383817311699444</v>
+        <v>0.1385006311783169</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -5699,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>55.25</v>
+        <v>56</v>
       </c>
       <c r="Y51" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z51" t="n">
         <v>60</v>
@@ -5735,7 +5735,7 @@
         <v>0.09386618138140031</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2938478120558171</v>
+        <v>0.2882115283869602</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>96</v>
       </c>
       <c r="Q52" t="n">
-        <v>7.375</v>
+        <v>7.4375</v>
       </c>
       <c r="R52" t="n">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.142189359910784</v>
+        <v>0.1421897647040285</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -5802,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>55.75</v>
+        <v>56.25</v>
       </c>
       <c r="Y52" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z52" t="n">
         <v>60</v>
@@ -5838,7 +5838,7 @@
         <v>0.489148222275413</v>
       </c>
       <c r="C53" t="n">
-        <v>0.09921013655052739</v>
+        <v>0.1015550045296841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,16 +5882,16 @@
         <v>96</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1943123342723108</v>
+        <v>0.193291460324133</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>36.5</v>
+        <v>36.25</v>
       </c>
       <c r="Y53" t="n">
         <v>27</v>
       </c>
       <c r="Z53" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -5934,43 +5934,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sec56</t>
+          <t>sec58</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2003951605397189</v>
+        <v>0.04641586339648113</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1369319970209936</v>
+        <v>0.3688368283897112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Peripheral Limited-Impact Sectors</t>
+          <t>Emerging Leverage Sectors</t>
         </is>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="H54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1580315963085921</v>
+        <v>0.2163936752419151</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1435319271865541</v>
+        <v>0.1404549021370866</v>
       </c>
       <c r="M54" t="n">
         <v>0.5149786364148489</v>
@@ -5985,16 +5985,16 @@
         <v>96</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="R54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0.1136185154072324</v>
+        <v>0.0940877143467206</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -6008,16 +6008,16 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>37.25</v>
+        <v>23.25</v>
       </c>
       <c r="Y54" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Z54" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.016</v>
+        <v>0.1021</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -6037,31 +6037,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sec58</t>
+          <t>sec24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.04641586339648113</v>
+        <v>0.787840880884735</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3774242545712791</v>
+        <v>0.02334507508805591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Emerging Leverage Sectors</t>
+          <t>Structurally Critical but Low-Transmission Sectors</t>
         </is>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0.2163936752419151</v>
       </c>
       <c r="K55" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1404549021370866</v>
+        <v>0.1323903860080543</v>
       </c>
       <c r="M55" t="n">
         <v>0.5149786364148489</v>
@@ -6088,16 +6088,16 @@
         <v>96</v>
       </c>
       <c r="Q55" t="n">
-        <v>7.0625</v>
+        <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.09552794800420635</v>
+        <v>0.2474644865638617</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -6111,16 +6111,16 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y55" t="n">
         <v>12</v>
       </c>
       <c r="Z55" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.1166</v>
+        <v>0.1607</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -6140,43 +6140,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sec24</t>
+          <t>sec56</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.787840880884735</v>
+        <v>0.2003951605397189</v>
       </c>
       <c r="C56" t="n">
-        <v>0.03002413352658418</v>
+        <v>0.1365222462705548</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Structurally Critical but Low-Transmission Sectors</t>
+          <t>Peripheral Limited-Impact Sectors</t>
         </is>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.967741935483871</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2163936752419151</v>
+        <v>0.1478250224179303</v>
       </c>
       <c r="K56" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1323903860080543</v>
+        <v>0.1303641241121909</v>
       </c>
       <c r="M56" t="n">
         <v>0.5149786364148489</v>
@@ -6191,16 +6191,16 @@
         <v>96</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.0625</v>
+        <v>11.6875</v>
       </c>
       <c r="R56" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.2567355098446881</v>
+        <v>0.1036034084321247</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -6214,16 +6214,16 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>19.75</v>
+        <v>38.75</v>
       </c>
       <c r="Y56" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="Z56" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.1637</v>
+        <v>0.004</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
@@ -6250,7 +6250,7 @@
         <v>0.03847697442290725</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4267791127204308</v>
+        <v>0.4184397474306021</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>0.7903225806451613</v>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>96</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.8125</v>
+        <v>6.0625</v>
       </c>
       <c r="R57" t="n">
         <v>6</v>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>0.08515474099026865</v>
+        <v>0.08539508806342501</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>59.5</v>
+        <v>58.75</v>
       </c>
       <c r="Y57" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z57" t="n">
         <v>61</v>
@@ -6353,7 +6353,7 @@
         <v>0.3450764124632084</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0836463505619668</v>
+        <v>0.08617070901936748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>0.06451612903225806</v>
       </c>
       <c r="H58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -6397,7 +6397,7 @@
         <v>96</v>
       </c>
       <c r="Q58" t="n">
-        <v>10.125</v>
+        <v>10</v>
       </c>
       <c r="R58" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.141098130575199</v>
+        <v>0.1422255302805292</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -6420,10 +6420,10 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>46.5</v>
+        <v>48.25</v>
       </c>
       <c r="Y58" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Z58" t="n">
         <v>60</v>
@@ -6456,7 +6456,7 @@
         <v>0.1829551495044086</v>
       </c>
       <c r="C59" t="n">
-        <v>0.100951623676353</v>
+        <v>0.1039019712316544</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>0.09677419354838709</v>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -6500,16 +6500,16 @@
         <v>96</v>
       </c>
       <c r="Q59" t="n">
-        <v>11.75</v>
+        <v>11.6875</v>
       </c>
       <c r="R59" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.1057033243151578</v>
+        <v>0.1063358784951333</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -6523,13 +6523,13 @@
         <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Y59" t="n">
         <v>36</v>
       </c>
       <c r="Z59" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -6552,14 +6552,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sec27</t>
+          <t>sec15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5405991449552966</v>
+        <v>0.7114828703891751</v>
       </c>
       <c r="C60" t="n">
-        <v>0.02431435161912338</v>
+        <v>0.009956328699082067</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6570,25 +6570,25 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="G60" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1644845004384769</v>
+        <v>0.1752061369548422</v>
       </c>
       <c r="K60" t="n">
         <v>0.03225806451612903</v>
       </c>
       <c r="L60" t="n">
-        <v>0.09837128247730298</v>
+        <v>0.1037321007354856</v>
       </c>
       <c r="M60" t="n">
         <v>0.5149786364148489</v>
@@ -6603,16 +6603,16 @@
         <v>96</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6875</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2132178645567819</v>
+        <v>0.07688283499193102</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -6623,22 +6623,22 @@
         </is>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" t="n">
-        <v>24.5</v>
+        <v>20</v>
       </c>
       <c r="Y60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z60" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0737</v>
+        <v>0.1022</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>10000</v>
@@ -6662,7 +6662,7 @@
         <v>0.02558335636244228</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2381736346885583</v>
+        <v>0.2360521602645237</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>96</v>
       </c>
       <c r="Q61" t="n">
-        <v>9.4375</v>
+        <v>9.375</v>
       </c>
       <c r="R61" t="n">
         <v>9</v>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0.07092417152818112</v>
+        <v>0.07155870592024728</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>61.25</v>
+        <v>61</v>
       </c>
       <c r="Y61" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z61" t="n">
         <v>62</v>
@@ -6758,11 +6758,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sec15</t>
+          <t>sec27</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7114828703891751</v>
+        <v>0.5405991449552966</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
@@ -6776,25 +6776,25 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="G62" t="n">
         <v>0.01612903225806452</v>
       </c>
       <c r="H62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1238894475462679</v>
+        <v>0.1163081056601287</v>
       </c>
       <c r="K62" t="n">
         <v>0.01612903225806452</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0700092399021662</v>
+        <v>0.0662185689590966</v>
       </c>
       <c r="M62" t="n">
         <v>0.5149786364148489</v>
@@ -6809,16 +6809,16 @@
         <v>96</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.25</v>
+        <v>3.9375</v>
       </c>
       <c r="R62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0.06886275228416799</v>
+        <v>0.2328331737060717</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="Y62" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Z62" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.1317</v>
+        <v>0.0583</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -6868,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1933734694896495</v>
+        <v>0.1936678759322911</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>96</v>
       </c>
       <c r="Q63" t="n">
-        <v>10.875</v>
+        <v>11.0625</v>
       </c>
       <c r="R63" t="n">
         <v>11</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.01958254123817594</v>
+        <v>0.01893158225524793</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>32.25</v>
+        <v>32.5</v>
       </c>
       <c r="Y63" t="n">
         <v>23</v>
@@ -6944,7 +6944,7 @@
         <v>46</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.0319</v>
+        <v>0.0396</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0.9991025623614186</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6807152591960837</v>
+        <v>0.6673676674308086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>0.9838709677419355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -7221,13 +7221,13 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9510659992132624</v>
+        <v>0.9593724101911646</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9352104189614698</v>
+        <v>0.9474281405794532</v>
       </c>
       <c r="M2" t="n">
         <v>0.5149786364148489</v>
@@ -7251,7 +7251,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8398321596762245</v>
+        <v>0.851703523715019</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -7277,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7552</v>
+        <v>0.8013</v>
       </c>
       <c r="AC2" t="n">
         <v>10000</v>
@@ -7301,7 +7301,7 @@
         <v>0.5192477741383978</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9532967073477324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -7324,13 +7324,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8980265101338745</v>
+        <v>0.8907549207409081</v>
       </c>
       <c r="K3" t="n">
         <v>0.8064516129032258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8522390615185501</v>
+        <v>0.8486032668220669</v>
       </c>
       <c r="M3" t="n">
         <v>0.5149786364148489</v>
@@ -7354,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7169949325357213</v>
+        <v>0.715544534416482</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -7368,19 +7368,19 @@
         <v>4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
         <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8998</v>
+        <v>0.781</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0776</v>
+        <v>0.0565</v>
       </c>
       <c r="AC3" t="n">
         <v>10000</v>
